--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124781924</v>
+        <v>124779833</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488809</v>
+        <v>489073</v>
       </c>
       <c r="R3" t="n">
-        <v>6849576</v>
+        <v>6849353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124779833</v>
+        <v>124781924</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489073</v>
+        <v>488809</v>
       </c>
       <c r="R4" t="n">
-        <v>6849353</v>
+        <v>6849576</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124782403</v>
+        <v>124779833</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488819</v>
+        <v>489073</v>
       </c>
       <c r="R2" t="n">
-        <v>6849386</v>
+        <v>6849353</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124779833</v>
+        <v>124782403</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489073</v>
+        <v>488819</v>
       </c>
       <c r="R3" t="n">
-        <v>6849353</v>
+        <v>6849386</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124779833</v>
+        <v>124782403</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489073</v>
+        <v>488819</v>
       </c>
       <c r="R2" t="n">
-        <v>6849353</v>
+        <v>6849386</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124782403</v>
+        <v>124779833</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488819</v>
+        <v>489073</v>
       </c>
       <c r="R3" t="n">
-        <v>6849386</v>
+        <v>6849353</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124782403</v>
+        <v>124781924</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488819</v>
+        <v>488809</v>
       </c>
       <c r="R2" t="n">
-        <v>6849386</v>
+        <v>6849576</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124781924</v>
+        <v>124782403</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488809</v>
+        <v>488819</v>
       </c>
       <c r="R4" t="n">
-        <v>6849576</v>
+        <v>6849386</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124781924</v>
+        <v>124782403</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488809</v>
+        <v>488819</v>
       </c>
       <c r="R2" t="n">
-        <v>6849576</v>
+        <v>6849386</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124782403</v>
+        <v>124781924</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488819</v>
+        <v>488809</v>
       </c>
       <c r="R4" t="n">
-        <v>6849386</v>
+        <v>6849576</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124782403</v>
+        <v>124779833</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488819</v>
+        <v>489073</v>
       </c>
       <c r="R2" t="n">
-        <v>6849386</v>
+        <v>6849353</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124779833</v>
+        <v>124781924</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489073</v>
+        <v>488809</v>
       </c>
       <c r="R3" t="n">
-        <v>6849353</v>
+        <v>6849576</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124781924</v>
+        <v>124782403</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488809</v>
+        <v>488819</v>
       </c>
       <c r="R4" t="n">
-        <v>6849576</v>
+        <v>6849386</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124779833</v>
+        <v>124781924</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489073</v>
+        <v>488809</v>
       </c>
       <c r="R2" t="n">
-        <v>6849353</v>
+        <v>6849576</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124781924</v>
+        <v>124782403</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488809</v>
+        <v>488819</v>
       </c>
       <c r="R3" t="n">
-        <v>6849576</v>
+        <v>6849386</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124782403</v>
+        <v>124779833</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488819</v>
+        <v>489073</v>
       </c>
       <c r="R4" t="n">
-        <v>6849386</v>
+        <v>6849353</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124781924</v>
+        <v>124779833</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vålberget, Dlr</t>
+          <t>Vålberget, Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488809</v>
+        <v>489073</v>
       </c>
       <c r="R2" t="n">
-        <v>6849576</v>
+        <v>6849353</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124779833</v>
+        <v>124781924</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vålberget, Vålberget, Dlr</t>
+          <t>Vålberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489073</v>
+        <v>488809</v>
       </c>
       <c r="R4" t="n">
-        <v>6849353</v>
+        <v>6849576</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29692-2020 artfynd.xlsx
+++ b/artfynd/A 29692-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124779833</v>
+        <v>124782403</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489073</v>
+        <v>488819</v>
       </c>
       <c r="R2" t="n">
-        <v>6849353</v>
+        <v>6849386</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124782403</v>
+        <v>124779833</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488819</v>
+        <v>489073</v>
       </c>
       <c r="R3" t="n">
-        <v>6849386</v>
+        <v>6849353</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,7 +882,7 @@
         <v>124781924</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
